--- a/docs/TestExecutionReport.xlsx
+++ b/docs/TestExecutionReport.xlsx
@@ -695,22 +695,22 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>42.56</v>
+        <v>22.88</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>43.82</v>
+        <v>23.86</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85.23%</t>
+          <t>94.89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Recovered via replica failover.</t>
+          <t>Recovered via replica failover. Median of 3 runs (MTTR 23.53-30.5 s).</t>
         </is>
       </c>
     </row>
@@ -736,22 +736,22 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>22.89</v>
+        <v>22.95</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>23.64</v>
+        <v>23.68</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>94.96%</t>
+          <t>94.89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Recovered via replica failover.</t>
+          <t>Recovered via replica failover. Median of 3 runs (MTTR 23.67-23.95 s).</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Zero downtime - replica served throughout.</t>
+          <t>Zero downtime - replica served throughout. Median of 3 runs.</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Zero downtime - replica served throughout.</t>
+          <t>Zero downtime - replica served throughout. Median of 3 runs.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Zero downtime - replica served throughout.</t>
+          <t>Zero downtime - replica served throughout. Median of 3 runs.</t>
         </is>
       </c>
     </row>
@@ -888,22 +888,22 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.06</v>
+        <v>0.45</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>42.53</v>
+        <v>22.91</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>43.69</v>
+        <v>23.91</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83.75%</t>
+          <t>94.89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Recovered via replica failover.</t>
+          <t>Recovered via replica failover. Median of 3 runs (MTTR 23.88-43.97 s).</t>
         </is>
       </c>
     </row>

--- a/docs/TestExecutionReport.xlsx
+++ b/docs/TestExecutionReport.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1070,6 +1070,37 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TC-CFG-001</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Configuration change: set a service config variable, apply and restart all; the value takes effect and all services return Online.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Config change applied after restart; all services returned Online (reverted after).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
